--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411551</v>
+        <v>124411541</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,43 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482698</v>
+        <v>482789</v>
       </c>
       <c r="R7" t="n">
-        <v>6951313</v>
+        <v>6951678</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,7 +1325,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gammalt gnag.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,7 +1334,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1362,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124411541</v>
+        <v>124411551</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>8447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,34 +1368,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482789</v>
+        <v>482698</v>
       </c>
       <c r="R8" t="n">
-        <v>6951678</v>
+        <v>6951313</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1441,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Gammalt gnag.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,6 +1450,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411541</v>
+        <v>124411551</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>8447</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1261,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482789</v>
+        <v>482698</v>
       </c>
       <c r="R7" t="n">
-        <v>6951678</v>
+        <v>6951313</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1334,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Gammalt gnag.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,6 +1343,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1352,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124411551</v>
+        <v>124411541</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,43 +1378,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482698</v>
+        <v>482789</v>
       </c>
       <c r="R8" t="n">
-        <v>6951313</v>
+        <v>6951678</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammalt gnag.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,7 +1451,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411551</v>
+        <v>124411541</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,43 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482698</v>
+        <v>482789</v>
       </c>
       <c r="R7" t="n">
-        <v>6951313</v>
+        <v>6951678</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,7 +1325,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gammalt gnag.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,7 +1334,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1362,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124411541</v>
+        <v>124411550</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>8447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,34 +1368,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482789</v>
+        <v>482733</v>
       </c>
       <c r="R8" t="n">
-        <v>6951678</v>
+        <v>6951336</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1441,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Gammalt gnag.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,6 +1450,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124411550</v>
+        <v>124411551</v>
       </c>
       <c r="B9" t="n">
         <v>8447</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482733</v>
+        <v>482698</v>
       </c>
       <c r="R9" t="n">
-        <v>6951336</v>
+        <v>6951313</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411541</v>
+        <v>124411550</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>8447</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1261,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482789</v>
+        <v>482733</v>
       </c>
       <c r="R7" t="n">
-        <v>6951678</v>
+        <v>6951336</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1334,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Gammalt gnag.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,6 +1343,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1352,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124411550</v>
+        <v>124411541</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,43 +1378,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482733</v>
+        <v>482789</v>
       </c>
       <c r="R8" t="n">
-        <v>6951336</v>
+        <v>6951678</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammalt gnag.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,7 +1451,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124411548</v>
+        <v>124411551</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>8447</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1159,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482714</v>
+        <v>482698</v>
       </c>
       <c r="R6" t="n">
-        <v>6951468</v>
+        <v>6951313</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,12 +1230,18 @@
           <t>2023-04-22</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1245,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411550</v>
+        <v>124411548</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,43 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482733</v>
+        <v>482714</v>
       </c>
       <c r="R7" t="n">
-        <v>6951336</v>
+        <v>6951468</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1332,18 +1338,12 @@
           <t>2023-04-22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124411551</v>
+        <v>124411550</v>
       </c>
       <c r="B9" t="n">
         <v>8447</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482698</v>
+        <v>482733</v>
       </c>
       <c r="R9" t="n">
-        <v>6951313</v>
+        <v>6951336</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411548</v>
+        <v>124411541</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482714</v>
+        <v>482789</v>
       </c>
       <c r="R7" t="n">
-        <v>6951468</v>
+        <v>6951678</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1336,6 +1336,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124411541</v>
+        <v>124411548</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>92293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482789</v>
+        <v>482714</v>
       </c>
       <c r="R8" t="n">
-        <v>6951678</v>
+        <v>6951468</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1438,11 +1443,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-04-22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124411551</v>
+        <v>124411550</v>
       </c>
       <c r="B6" t="n">
         <v>8447</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482698</v>
+        <v>482733</v>
       </c>
       <c r="R6" t="n">
-        <v>6951313</v>
+        <v>6951336</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411541</v>
+        <v>124411548</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482789</v>
+        <v>482714</v>
       </c>
       <c r="R7" t="n">
-        <v>6951678</v>
+        <v>6951468</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1336,11 +1336,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-04-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124411548</v>
+        <v>124411541</v>
       </c>
       <c r="B8" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482714</v>
+        <v>482789</v>
       </c>
       <c r="R8" t="n">
-        <v>6951468</v>
+        <v>6951678</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1443,6 +1438,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124411550</v>
+        <v>124411551</v>
       </c>
       <c r="B9" t="n">
         <v>8447</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482733</v>
+        <v>482698</v>
       </c>
       <c r="R9" t="n">
-        <v>6951336</v>
+        <v>6951313</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124411550</v>
+        <v>124411548</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,43 +1159,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482733</v>
+        <v>482714</v>
       </c>
       <c r="R6" t="n">
-        <v>6951336</v>
+        <v>6951468</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1230,18 +1221,12 @@
           <t>2023-04-22</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411548</v>
+        <v>124411550</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>8447</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1261,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482714</v>
+        <v>482733</v>
       </c>
       <c r="R7" t="n">
-        <v>6951468</v>
+        <v>6951336</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1338,12 +1332,18 @@
           <t>2023-04-22</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124411548</v>
+        <v>124411541</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482714</v>
+        <v>482789</v>
       </c>
       <c r="R6" t="n">
-        <v>6951468</v>
+        <v>6951678</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1219,6 +1219,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411550</v>
+        <v>124411551</v>
       </c>
       <c r="B7" t="n">
         <v>8447</v>
@@ -1294,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482733</v>
+        <v>482698</v>
       </c>
       <c r="R7" t="n">
-        <v>6951336</v>
+        <v>6951313</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1362,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124411541</v>
+        <v>124411550</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>8447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,34 +1383,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482789</v>
+        <v>482733</v>
       </c>
       <c r="R8" t="n">
-        <v>6951678</v>
+        <v>6951336</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1456,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Gammalt gnag.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,6 +1465,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1469,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124411551</v>
+        <v>124411548</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>92293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,43 +1500,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482698</v>
+        <v>482714</v>
       </c>
       <c r="R9" t="n">
-        <v>6951313</v>
+        <v>6951468</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1556,18 +1562,12 @@
           <t>2023-04-22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124411541</v>
+        <v>124411551</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>8447</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1159,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482789</v>
+        <v>482698</v>
       </c>
       <c r="R6" t="n">
-        <v>6951678</v>
+        <v>6951313</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,7 +1232,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Gammalt gnag.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,6 +1241,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411551</v>
+        <v>124411541</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,43 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482698</v>
+        <v>482789</v>
       </c>
       <c r="R7" t="n">
-        <v>6951313</v>
+        <v>6951678</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1339,7 +1340,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gammalt gnag.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,7 +1349,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124411551</v>
+        <v>124411548</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,43 +1159,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482698</v>
+        <v>482714</v>
       </c>
       <c r="R6" t="n">
-        <v>6951313</v>
+        <v>6951468</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1230,18 +1221,12 @@
           <t>2023-04-22</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1367,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124411550</v>
+        <v>124411551</v>
       </c>
       <c r="B8" t="n">
         <v>8447</v>
@@ -1416,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482733</v>
+        <v>482698</v>
       </c>
       <c r="R8" t="n">
-        <v>6951336</v>
+        <v>6951313</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1484,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124411548</v>
+        <v>124411550</v>
       </c>
       <c r="B9" t="n">
-        <v>92293</v>
+        <v>8447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,34 +1485,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482714</v>
+        <v>482733</v>
       </c>
       <c r="R9" t="n">
-        <v>6951468</v>
+        <v>6951336</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1562,12 +1556,18 @@
           <t>2023-04-22</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411541</v>
+        <v>124411550</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>8447</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1261,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482789</v>
+        <v>482733</v>
       </c>
       <c r="R7" t="n">
-        <v>6951678</v>
+        <v>6951336</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1334,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Gammalt gnag.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,6 +1343,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1352,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124411551</v>
+        <v>124411541</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,43 +1378,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482698</v>
+        <v>482789</v>
       </c>
       <c r="R8" t="n">
-        <v>6951313</v>
+        <v>6951678</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,7 +1442,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gammalt gnag.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,7 +1451,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124411550</v>
+        <v>124411551</v>
       </c>
       <c r="B9" t="n">
         <v>8447</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482733</v>
+        <v>482698</v>
       </c>
       <c r="R9" t="n">
-        <v>6951336</v>
+        <v>6951313</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411550</v>
+        <v>124411541</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,43 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482733</v>
+        <v>482789</v>
       </c>
       <c r="R7" t="n">
-        <v>6951336</v>
+        <v>6951678</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,7 +1325,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gammalt gnag.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,7 +1334,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1362,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124411541</v>
+        <v>124411551</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>8447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,34 +1368,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482789</v>
+        <v>482698</v>
       </c>
       <c r="R8" t="n">
-        <v>6951678</v>
+        <v>6951313</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1441,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Gammalt gnag.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,6 +1450,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124411551</v>
+        <v>124411550</v>
       </c>
       <c r="B9" t="n">
         <v>8447</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482698</v>
+        <v>482733</v>
       </c>
       <c r="R9" t="n">
-        <v>6951313</v>
+        <v>6951336</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124411548</v>
+        <v>124411541</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482714</v>
+        <v>482789</v>
       </c>
       <c r="R6" t="n">
-        <v>6951468</v>
+        <v>6951678</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1219,6 +1219,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411541</v>
+        <v>124411550</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>8447</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1266,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482789</v>
+        <v>482733</v>
       </c>
       <c r="R7" t="n">
-        <v>6951678</v>
+        <v>6951336</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1339,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Gammalt gnag.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,6 +1348,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1352,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124411551</v>
+        <v>124411548</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>92293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,43 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482698</v>
+        <v>482714</v>
       </c>
       <c r="R8" t="n">
-        <v>6951313</v>
+        <v>6951468</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1439,18 +1445,12 @@
           <t>2023-04-22</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124411550</v>
+        <v>124411551</v>
       </c>
       <c r="B9" t="n">
         <v>8447</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482733</v>
+        <v>482698</v>
       </c>
       <c r="R9" t="n">
-        <v>6951336</v>
+        <v>6951313</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124411541</v>
+        <v>124411550</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>8447</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1159,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482789</v>
+        <v>482733</v>
       </c>
       <c r="R6" t="n">
-        <v>6951678</v>
+        <v>6951336</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,7 +1232,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>Gammalt gnag.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,6 +1241,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411550</v>
+        <v>124411548</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,43 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482733</v>
+        <v>482714</v>
       </c>
       <c r="R7" t="n">
-        <v>6951336</v>
+        <v>6951468</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1337,18 +1338,12 @@
           <t>2023-04-22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1367,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124411548</v>
+        <v>124411541</v>
       </c>
       <c r="B8" t="n">
-        <v>92293</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482714</v>
+        <v>482789</v>
       </c>
       <c r="R8" t="n">
-        <v>6951468</v>
+        <v>6951678</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1443,6 +1438,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1584,6 +1584,670 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128159853</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>482556</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6951556</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i tall.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128159857</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5493</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>482295</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6951820</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128159836</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5493</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>482419</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6951706</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128159855</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79998</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>388</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stiftgelélav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>482526</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6951637</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Klen asp i torr tallskog.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128159838</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5493</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>482396</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6951811</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128159848</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5493</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>482381</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6951731</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1586,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128159853</v>
+        <v>128159857</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>5493</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,24 +1597,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>101410</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -1625,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482556</v>
+        <v>482295</v>
       </c>
       <c r="R10" t="n">
-        <v>6951556</v>
+        <v>6951820</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1666,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gamla ringhack i tall.</t>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,6 +1675,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1696,7 +1698,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128159857</v>
+        <v>128159836</v>
       </c>
       <c r="B11" t="n">
         <v>5493</v>
@@ -1736,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482295</v>
+        <v>482419</v>
       </c>
       <c r="R11" t="n">
-        <v>6951820</v>
+        <v>6951706</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1808,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128159836</v>
+        <v>128159855</v>
       </c>
       <c r="B12" t="n">
-        <v>5493</v>
+        <v>79998</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,39 +1821,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>388</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482419</v>
+        <v>482526</v>
       </c>
       <c r="R12" t="n">
-        <v>6951706</v>
+        <v>6951637</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,7 +1885,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Klen asp i torr tallskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,7 +1894,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1920,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128159855</v>
+        <v>128159838</v>
       </c>
       <c r="B13" t="n">
-        <v>79998</v>
+        <v>5493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,34 +1927,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>388</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482526</v>
+        <v>482396</v>
       </c>
       <c r="R13" t="n">
-        <v>6951637</v>
+        <v>6951811</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1996,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Klen asp i torr tallskog.</t>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,6 +2005,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2026,7 +2028,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128159838</v>
+        <v>128159848</v>
       </c>
       <c r="B14" t="n">
         <v>5493</v>
@@ -2066,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482396</v>
+        <v>482381</v>
       </c>
       <c r="R14" t="n">
-        <v>6951811</v>
+        <v>6951731</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128159848</v>
+        <v>128159853</v>
       </c>
       <c r="B15" t="n">
-        <v>5493</v>
+        <v>57673</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2149,25 +2151,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101410</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -2178,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482381</v>
+        <v>482556</v>
       </c>
       <c r="R15" t="n">
-        <v>6951731</v>
+        <v>6951556</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,7 +2219,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Gamla ringhack i tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,7 +2228,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1813,7 +1813,7 @@
         <v>128159855</v>
       </c>
       <c r="B12" t="n">
-        <v>79998</v>
+        <v>80001</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1813,7 +1813,7 @@
         <v>128159855</v>
       </c>
       <c r="B12" t="n">
-        <v>80001</v>
+        <v>80054</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -2143,7 +2143,7 @@
         <v>128159853</v>
       </c>
       <c r="B15" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -2143,7 +2143,7 @@
         <v>128159853</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1813,7 +1813,7 @@
         <v>128159855</v>
       </c>
       <c r="B12" t="n">
-        <v>80054</v>
+        <v>80058</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -1813,7 +1813,7 @@
         <v>128159855</v>
       </c>
       <c r="B12" t="n">
-        <v>80058</v>
+        <v>80060</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -2143,7 +2143,7 @@
         <v>128159853</v>
       </c>
       <c r="B15" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2248,6 +2248,208 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128869307</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79215</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>967</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Varglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Letharia vulpina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>483128</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6951573</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128869309</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79710</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>483128</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6951573</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -2143,7 +2143,7 @@
         <v>128159853</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>128869307</v>
       </c>
       <c r="B16" t="n">
-        <v>79215</v>
+        <v>79219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128869309</v>
       </c>
       <c r="B17" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -2143,7 +2143,7 @@
         <v>128159853</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>128869307</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128869309</v>
       </c>
       <c r="B17" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -2253,7 +2253,7 @@
         <v>128869307</v>
       </c>
       <c r="B16" t="n">
-        <v>79129</v>
+        <v>79130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128869309</v>
       </c>
       <c r="B17" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -2253,7 +2253,7 @@
         <v>128869307</v>
       </c>
       <c r="B16" t="n">
-        <v>79130</v>
+        <v>79134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128869309</v>
       </c>
       <c r="B17" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -2253,7 +2253,7 @@
         <v>128869307</v>
       </c>
       <c r="B16" t="n">
-        <v>79134</v>
+        <v>79136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128869309</v>
       </c>
       <c r="B17" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -2253,7 +2253,7 @@
         <v>128869307</v>
       </c>
       <c r="B16" t="n">
-        <v>79136</v>
+        <v>79138</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>128869309</v>
       </c>
       <c r="B17" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103968252</v>
+        <v>128159855</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Hackåstjärnen, Jmt</t>
+          <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482777.0470209528</v>
+        <v>482526</v>
       </c>
       <c r="R2" t="n">
-        <v>6951257.443675355</v>
+        <v>6951637</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Klen asp i torr tallskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -785,26 +770,21 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Pär Hedberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108245598</v>
+        <v>128869307</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,31 +792,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,13 +819,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482897.9266703781</v>
+        <v>483128</v>
       </c>
       <c r="R3" t="n">
-        <v>6951335.79172979</v>
+        <v>6951573</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,27 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på klen tall</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -921,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115969946</v>
+        <v>124411553</v>
       </c>
       <c r="B4" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,40 +893,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Näktesberget, Jmt</t>
+          <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>482954</v>
+        <v>482732</v>
       </c>
       <c r="R4" t="n">
-        <v>6951470</v>
+        <v>6951257</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,17 +947,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På torraka av tall.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,15 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115969942</v>
+        <v>103968252</v>
       </c>
       <c r="B5" t="n">
-        <v>77446</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,37 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Näktesberget, Jmt</t>
+          <t>Lill-Hackåstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>482954</v>
+        <v>482777</v>
       </c>
       <c r="R5" t="n">
-        <v>6951470</v>
+        <v>6951258</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,17 +1050,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På torraka av tall.</t>
+          <t>2022-06-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,9 +1074,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1136,66 +1090,56 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124411550</v>
+        <v>124411548</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>482733</v>
+        <v>482714</v>
       </c>
       <c r="R6" t="n">
-        <v>6951336</v>
+        <v>6951468</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1230,18 +1174,12 @@
           <t>2023-04-22</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,19 +1198,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124411548</v>
+        <v>124411549</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1300,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>482714</v>
+        <v>482711</v>
       </c>
       <c r="R7" t="n">
-        <v>6951468</v>
+        <v>6951440</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1362,37 +1295,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124411541</v>
+        <v>124411552</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>482789</v>
+        <v>482718</v>
       </c>
       <c r="R8" t="n">
-        <v>6951678</v>
+        <v>6951273</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1370,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälg.</t>
+          <t>På kolad högstubbe som har spår från minst två bränder.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,59 +1397,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124411551</v>
+        <v>124411545</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>482698</v>
+        <v>483077</v>
       </c>
       <c r="R9" t="n">
-        <v>6951313</v>
+        <v>6951648</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,7 +1472,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gammalt gnag.</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,7 +1481,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1586,53 +1499,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128159857</v>
+        <v>124411541</v>
       </c>
       <c r="B10" t="n">
-        <v>5493</v>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101410</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>482295</v>
+        <v>482789</v>
       </c>
       <c r="R10" t="n">
-        <v>6951820</v>
+        <v>6951678</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1656,17 +1564,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,7 +1583,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1687,21 +1594,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128159836</v>
+        <v>115969942</v>
       </c>
       <c r="B11" t="n">
-        <v>5493</v>
+        <v>78334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,39 +1612,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101410</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näktesbergen, Jmt</t>
+          <t>Näktesberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>482419</v>
+        <v>482954</v>
       </c>
       <c r="R11" t="n">
-        <v>6951706</v>
+        <v>6951470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,17 +1669,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>På torraka av tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,21 +1700,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128159855</v>
+        <v>108245598</v>
       </c>
       <c r="B12" t="n">
-        <v>80060</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,34 +1718,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>388</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>482526</v>
+        <v>482898</v>
       </c>
       <c r="R12" t="n">
-        <v>6951637</v>
+        <v>6951336</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,17 +1780,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Klen asp i torr tallskog.</t>
+          <t>Ringhack på klen tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,21 +1810,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128159838</v>
+        <v>128159853</v>
       </c>
       <c r="B13" t="n">
-        <v>5493</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,25 +1828,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -1956,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>482396</v>
+        <v>482556</v>
       </c>
       <c r="R13" t="n">
-        <v>6951811</v>
+        <v>6951556</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,7 +1896,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Gamla ringhack i tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,7 +1905,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2028,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128159848</v>
+        <v>128159836</v>
       </c>
       <c r="B14" t="n">
-        <v>5493</v>
+        <v>5495</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>482381</v>
+        <v>482419</v>
       </c>
       <c r="R14" t="n">
-        <v>6951731</v>
+        <v>6951706</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128159853</v>
+        <v>128159838</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>5495</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,24 +2050,25 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>101410</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -2179,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>482556</v>
+        <v>482396</v>
       </c>
       <c r="R15" t="n">
-        <v>6951556</v>
+        <v>6951811</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2119,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gamla ringhack i tall.</t>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,6 +2128,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2250,10 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128869307</v>
+        <v>128159848</v>
       </c>
       <c r="B16" t="n">
-        <v>79138</v>
+        <v>5495</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,26 +2162,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>967</v>
+        <v>101410</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2288,13 +2191,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483128</v>
+        <v>482381</v>
       </c>
       <c r="R16" t="n">
-        <v>6951573</v>
+        <v>6951731</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,12 +2221,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,17 +2252,21 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128869309</v>
+        <v>128159857</v>
       </c>
       <c r="B17" t="n">
-        <v>79633</v>
+        <v>5495</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,26 +2274,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>101410</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2389,13 +2303,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483128</v>
+        <v>482295</v>
       </c>
       <c r="R17" t="n">
-        <v>6951573</v>
+        <v>6951820</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2419,12 +2333,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2445,10 +2364,542 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124411550</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>482733</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6951336</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124411551</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>482698</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6951313</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>115969946</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Näktesberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>482954</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6951470</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På torraka av tall.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124411555</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>482805</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6951233</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-04-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128869309</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>483128</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6951573</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7473-2023 artfynd.xlsx
+++ b/artfynd/A 7473-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128159855</t>
         </is>
       </c>
     </row>
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128869307</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124411553</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968252</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124411548</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124411549</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124411552</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124411545</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1598,6 +1643,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124411541</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1704,6 +1754,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115969942</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108245598</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1922,6 +1982,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128159853</t>
         </is>
       </c>
     </row>
@@ -2036,6 +2101,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128159836</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2148,6 +2218,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128159838</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2260,6 +2335,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128159848</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2372,6 +2452,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128159857</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2484,6 +2569,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124411550</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2596,6 +2686,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124411551</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2702,6 +2797,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115969946</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2799,6 +2899,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124411555</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2900,8 +3005,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128869309</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>